--- a/appointment_forms/025_spa_appointment_form--appointment_forms.xlsx
+++ b/appointment_forms/025_spa_appointment_form--appointment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -575,7 +575,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -598,7 +598,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -621,7 +621,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -698,7 +698,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -744,7 +744,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Message</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Service Description</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Service Details</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Appointment Date</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -848,7 +848,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Appointment Time</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -871,7 +871,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Client Email</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -894,7 +894,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Client Phone</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -917,7 +917,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Staff Name</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -940,7 +940,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Staff Email</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -963,7 +963,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Staff Phone</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -981,12 +981,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>service_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Service 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Appointment Note</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Client Address</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>service_description</t>
+          <t>service_description_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Service Description 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Appointment Duration</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Staff</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1133,7 +1133,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1192,7 +1192,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>service_choices</t>
+          <t>service_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>service_choices</t>
+          <t>service_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
